--- a/2.Diseños/2.0_Patron_de_Diseño/GN2_Matriz de Marco de Trabajo HU_V.xlsx
+++ b/2.Diseños/2.0_Patron_de_Diseño/GN2_Matriz de Marco de Trabajo HU_V.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="115">
   <si>
     <t>Matriz de Marco de Trabajo de HU</t>
   </si>
@@ -352,6 +352,21 @@
   <si>
     <t>HISTORIA DE USUARIO (HU) RQ-04</t>
   </si>
+  <si>
+    <t>HISTORIA DE USUARIO (HU) RQ-05</t>
+  </si>
+  <si>
+    <t>HISTORIA DE USUARIO (HU) RQ-06</t>
+  </si>
+  <si>
+    <t>HISTORIA DE USUARIO (HU) RQ-07</t>
+  </si>
+  <si>
+    <t>HISTORIA DE USUARIO (HU) RQ-08</t>
+  </si>
+  <si>
+    <t>HISTORIA DE USUARIO (HU) RQ-10</t>
+  </si>
 </sst>
 </file>
 
@@ -361,7 +376,7 @@
     <numFmt numFmtId="164" formatCode="d/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -460,8 +475,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,6 +528,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FF5B9BD5"/>
       </patternFill>
     </fill>
   </fills>
@@ -790,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="120">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -975,17 +1007,95 @@
     <xf borderId="0" fillId="0" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="8" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="5" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="11" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="13" fillId="10" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="14" fillId="4" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="8" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="24" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="33" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="14" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="30" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="31" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="35" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="32" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1236,10 +1346,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1066800" cy="1162050"/>
     <xdr:pic>
@@ -31799,164 +31909,2159 @@
       <c r="P102" s="31"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="B103" s="31"/>
-      <c r="C103" s="31"/>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31"/>
-      <c r="F103" s="31"/>
-      <c r="G103" s="31"/>
-      <c r="H103" s="31"/>
-      <c r="I103" s="31"/>
-      <c r="J103" s="31"/>
-      <c r="K103" s="31"/>
-      <c r="L103" s="31"/>
-      <c r="M103" s="31"/>
-      <c r="N103" s="31"/>
-      <c r="O103" s="31"/>
-      <c r="P103" s="31"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="B104" s="31"/>
-      <c r="C104" s="31"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="31"/>
-      <c r="F104" s="31"/>
-      <c r="G104" s="31"/>
-      <c r="H104" s="31"/>
-      <c r="I104" s="31"/>
-      <c r="J104" s="31"/>
-      <c r="K104" s="31"/>
-      <c r="L104" s="31"/>
-      <c r="M104" s="31"/>
-      <c r="N104" s="31"/>
-      <c r="O104" s="31"/>
-      <c r="P104" s="31"/>
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="29"/>
+    </row>
+    <row r="104" ht="21.75" customHeight="1">
+      <c r="B104" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="6"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="B105" s="86"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
+      <c r="A105" s="31"/>
+      <c r="B105" s="31"/>
+      <c r="C105" s="32"/>
+      <c r="D105" s="32"/>
+      <c r="E105" s="32"/>
+      <c r="F105" s="32"/>
+      <c r="G105" s="32"/>
+      <c r="H105" s="32"/>
+      <c r="I105" s="32"/>
+      <c r="J105" s="32"/>
+      <c r="K105" s="32"/>
+      <c r="L105" s="32"/>
+      <c r="M105" s="32"/>
+      <c r="N105" s="32"/>
+      <c r="O105" s="32"/>
+      <c r="P105" s="31"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="B106" s="33"/>
+      <c r="C106" s="34"/>
+      <c r="D106" s="34"/>
+      <c r="E106" s="34"/>
+      <c r="F106" s="35"/>
+      <c r="G106" s="36"/>
+      <c r="H106" s="36"/>
+      <c r="I106" s="36"/>
+      <c r="J106" s="36"/>
+      <c r="K106" s="36"/>
+      <c r="L106" s="36"/>
+      <c r="M106" s="36"/>
+      <c r="N106" s="36"/>
+      <c r="O106" s="36"/>
+      <c r="P106" s="37"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="B107" s="38"/>
+      <c r="C107" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="40"/>
+      <c r="E107" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="F107" s="6"/>
+      <c r="G107" s="40"/>
+      <c r="H107" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I107" s="6"/>
+      <c r="J107" s="42"/>
+      <c r="K107" s="42"/>
+      <c r="L107" s="42"/>
+      <c r="M107" s="42"/>
+      <c r="N107" s="42"/>
+      <c r="O107" s="42"/>
+      <c r="P107" s="43"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="B108" s="38"/>
+      <c r="C108" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D108" s="45"/>
+      <c r="E108" s="46" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,5,0)</f>
+        <v>Entrenador</v>
+      </c>
+      <c r="F108" s="6"/>
+      <c r="G108" s="47"/>
+      <c r="H108" s="46" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,11,0)</f>
+        <v>En proceso</v>
+      </c>
+      <c r="I108" s="6"/>
+      <c r="J108" s="47"/>
+      <c r="K108" s="42"/>
+      <c r="L108" s="42"/>
+      <c r="M108" s="42"/>
+      <c r="N108" s="42"/>
+      <c r="O108" s="42"/>
+      <c r="P108" s="43"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="31"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="48"/>
+      <c r="D109" s="45"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="47"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="49"/>
+      <c r="J109" s="47"/>
+      <c r="K109" s="49"/>
+      <c r="L109" s="49"/>
+      <c r="M109" s="42"/>
+      <c r="N109" s="49"/>
+      <c r="O109" s="49"/>
+      <c r="P109" s="43"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="31"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D110" s="45"/>
+      <c r="E110" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="6"/>
+      <c r="G110" s="47"/>
+      <c r="H110" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="I110" s="6"/>
+      <c r="J110" s="47"/>
+      <c r="K110" s="49"/>
+      <c r="L110" s="49"/>
+      <c r="M110" s="42"/>
+      <c r="N110" s="49"/>
+      <c r="O110" s="49"/>
+      <c r="P110" s="43"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="31"/>
+      <c r="B111" s="38"/>
+      <c r="C111" s="50">
+        <f>VLOOKUP('Historia de Usuario'!C108,'Formato descripción HU'!B10:O115,8,0)</f>
+        <v>6</v>
+      </c>
+      <c r="D111" s="45"/>
+      <c r="E111" s="46" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,10,0)</f>
+        <v>Alta</v>
+      </c>
+      <c r="F111" s="6"/>
+      <c r="G111" s="47"/>
+      <c r="H111" s="46" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,7,0)</f>
+        <v>Josué Solano</v>
+      </c>
+      <c r="I111" s="6"/>
+      <c r="J111" s="47"/>
+      <c r="K111" s="49"/>
+      <c r="L111" s="49"/>
+      <c r="M111" s="42"/>
+      <c r="N111" s="49"/>
+      <c r="O111" s="49"/>
+      <c r="P111" s="43"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="31"/>
+      <c r="B112" s="38"/>
+      <c r="C112" s="42"/>
+      <c r="D112" s="45"/>
+      <c r="E112" s="42"/>
+      <c r="F112" s="42"/>
+      <c r="G112" s="47"/>
+      <c r="H112" s="47"/>
+      <c r="I112" s="42"/>
+      <c r="J112" s="42"/>
+      <c r="K112" s="42"/>
+      <c r="L112" s="42"/>
+      <c r="M112" s="42"/>
+      <c r="N112" s="42"/>
+      <c r="O112" s="42"/>
+      <c r="P112" s="43"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="31"/>
+      <c r="B113" s="38"/>
+      <c r="C113" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D113" s="52" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,3,0)</f>
+        <v>Facilitar la comunicación interna</v>
+      </c>
+      <c r="E113" s="53"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H113" s="52" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,4,0)</f>
+        <v>Mejorar la interacción y seguimiento deportivo</v>
+      </c>
+      <c r="I113" s="55"/>
+      <c r="J113" s="53"/>
+      <c r="K113" s="54"/>
+      <c r="L113" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="M113" s="56" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,6,0)</f>
+        <v>Crear mensajes, enviar anuncios y consultar historial de comunicaciones</v>
+      </c>
+      <c r="N113" s="55"/>
+      <c r="O113" s="53"/>
+      <c r="P113" s="43"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="31"/>
+      <c r="B114" s="38"/>
+      <c r="C114" s="57"/>
+      <c r="D114" s="58"/>
+      <c r="E114" s="59"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="58"/>
+      <c r="J114" s="59"/>
+      <c r="K114" s="54"/>
+      <c r="L114" s="57"/>
+      <c r="M114" s="58"/>
+      <c r="O114" s="59"/>
+      <c r="P114" s="43"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="31"/>
+      <c r="B115" s="38"/>
+      <c r="C115" s="60"/>
+      <c r="D115" s="61"/>
+      <c r="E115" s="62"/>
+      <c r="F115" s="54"/>
+      <c r="G115" s="60"/>
+      <c r="H115" s="61"/>
+      <c r="I115" s="63"/>
+      <c r="J115" s="62"/>
+      <c r="K115" s="54"/>
+      <c r="L115" s="60"/>
+      <c r="M115" s="61"/>
+      <c r="N115" s="63"/>
+      <c r="O115" s="62"/>
+      <c r="P115" s="43"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="31"/>
+      <c r="B116" s="38"/>
+      <c r="C116" s="42"/>
+      <c r="D116" s="42"/>
+      <c r="E116" s="42"/>
+      <c r="F116" s="42"/>
+      <c r="G116" s="47"/>
+      <c r="H116" s="47"/>
+      <c r="I116" s="47"/>
+      <c r="J116" s="42"/>
+      <c r="K116" s="42"/>
+      <c r="L116" s="42"/>
+      <c r="M116" s="42"/>
+      <c r="N116" s="42"/>
+      <c r="O116" s="42"/>
+      <c r="P116" s="43"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="B117" s="38"/>
+      <c r="C117" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D117" s="53"/>
+      <c r="E117" s="65" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,14,0)</f>
+        <v>Comunicación con atletas</v>
+      </c>
+      <c r="F117" s="66"/>
+      <c r="G117" s="66"/>
+      <c r="H117" s="66"/>
+      <c r="I117" s="66"/>
+      <c r="J117" s="66"/>
+      <c r="K117" s="66"/>
+      <c r="L117" s="66"/>
+      <c r="M117" s="66"/>
+      <c r="N117" s="66"/>
+      <c r="O117" s="67"/>
+      <c r="P117" s="43"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="B118" s="38"/>
+      <c r="C118" s="61"/>
+      <c r="D118" s="62"/>
+      <c r="E118" s="68"/>
+      <c r="F118" s="69"/>
+      <c r="G118" s="69"/>
+      <c r="H118" s="69"/>
+      <c r="I118" s="69"/>
+      <c r="J118" s="69"/>
+      <c r="K118" s="69"/>
+      <c r="L118" s="69"/>
+      <c r="M118" s="69"/>
+      <c r="N118" s="69"/>
+      <c r="O118" s="70"/>
+      <c r="P118" s="43"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="B119" s="38"/>
+      <c r="C119" s="42"/>
+      <c r="D119" s="42"/>
+      <c r="E119" s="78"/>
+      <c r="F119" s="78"/>
+      <c r="G119" s="78"/>
+      <c r="H119" s="78"/>
+      <c r="I119" s="42"/>
+      <c r="J119" s="42"/>
+      <c r="K119" s="42"/>
+      <c r="L119" s="42"/>
+      <c r="M119" s="42"/>
+      <c r="N119" s="42"/>
+      <c r="O119" s="42"/>
+      <c r="P119" s="43"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="31"/>
+      <c r="B120" s="38"/>
+      <c r="C120" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D120" s="53"/>
+      <c r="E120" s="72" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,12,0)</f>
+        <v>Verificar el envío, recepción y visualización de mensajes entre usuarios.</v>
+      </c>
+      <c r="F120" s="55"/>
+      <c r="G120" s="55"/>
+      <c r="H120" s="53"/>
+      <c r="I120" s="79"/>
+      <c r="J120" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="K120" s="53"/>
+      <c r="L120" s="52" t="str">
+        <f>VLOOKUP(C108,'Formato descripción HU'!B10:O115,13,0)</f>
+        <v>Puede ampliarse posteriormente con notificaciones en tiempo real o correo electrónico.</v>
+      </c>
+      <c r="M120" s="55"/>
+      <c r="N120" s="55"/>
+      <c r="O120" s="53"/>
+      <c r="P120" s="43"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="31"/>
+      <c r="B121" s="38"/>
+      <c r="C121" s="58"/>
+      <c r="D121" s="59"/>
+      <c r="E121" s="58"/>
+      <c r="H121" s="59"/>
+      <c r="I121" s="79"/>
+      <c r="J121" s="58"/>
+      <c r="K121" s="59"/>
+      <c r="L121" s="58"/>
+      <c r="O121" s="59"/>
+      <c r="P121" s="43"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="31"/>
+      <c r="B122" s="38"/>
+      <c r="C122" s="61"/>
+      <c r="D122" s="62"/>
+      <c r="E122" s="61"/>
+      <c r="F122" s="63"/>
+      <c r="G122" s="63"/>
+      <c r="H122" s="62"/>
+      <c r="I122" s="79"/>
+      <c r="J122" s="61"/>
+      <c r="K122" s="62"/>
+      <c r="L122" s="61"/>
+      <c r="M122" s="63"/>
+      <c r="N122" s="63"/>
+      <c r="O122" s="62"/>
+      <c r="P122" s="43"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="31"/>
+      <c r="B123" s="73"/>
+      <c r="C123" s="74"/>
+      <c r="D123" s="74"/>
+      <c r="E123" s="81"/>
+      <c r="F123" s="81"/>
+      <c r="G123" s="81"/>
+      <c r="H123" s="81"/>
+      <c r="I123" s="74"/>
+      <c r="J123" s="74"/>
+      <c r="K123" s="74"/>
+      <c r="L123" s="74"/>
+      <c r="M123" s="74"/>
+      <c r="N123" s="74"/>
+      <c r="O123" s="74"/>
+      <c r="P123" s="75"/>
+    </row>
     <row r="124" ht="15.75" customHeight="1"/>
     <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="G127" s="77"/>
-      <c r="H127" s="87"/>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="86"/>
+      <c r="B126" s="86"/>
+      <c r="C126" s="87"/>
+      <c r="D126" s="87"/>
+      <c r="E126" s="87"/>
+      <c r="F126" s="86"/>
+      <c r="G126" s="86"/>
+      <c r="H126" s="86"/>
+      <c r="I126" s="86"/>
+      <c r="J126" s="86"/>
+      <c r="K126" s="86"/>
+      <c r="L126" s="86"/>
+      <c r="M126" s="86"/>
+      <c r="N126" s="86"/>
+      <c r="O126" s="86"/>
+      <c r="P126" s="86"/>
+    </row>
+    <row r="127" ht="22.5" customHeight="1">
+      <c r="A127" s="86"/>
+      <c r="B127" s="88" t="s">
+        <v>111</v>
+      </c>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="5"/>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5"/>
+      <c r="P127" s="6"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="G128" s="77"/>
-      <c r="H128" s="88"/>
+      <c r="A128" s="86"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="87"/>
+      <c r="D128" s="87"/>
+      <c r="E128" s="87"/>
+      <c r="F128" s="87"/>
+      <c r="G128" s="31"/>
+      <c r="H128" s="89"/>
+      <c r="I128" s="87"/>
+      <c r="J128" s="87"/>
+      <c r="K128" s="87"/>
+      <c r="L128" s="87"/>
+      <c r="M128" s="87"/>
+      <c r="N128" s="87"/>
+      <c r="O128" s="87"/>
+      <c r="P128" s="86"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="G129" s="77"/>
-      <c r="H129" s="89"/>
+      <c r="A129" s="86"/>
+      <c r="B129" s="90"/>
+      <c r="C129" s="91"/>
+      <c r="D129" s="91"/>
+      <c r="E129" s="91"/>
+      <c r="F129" s="92"/>
+      <c r="G129" s="93"/>
+      <c r="H129" s="93"/>
+      <c r="I129" s="92"/>
+      <c r="J129" s="92"/>
+      <c r="K129" s="92"/>
+      <c r="L129" s="92"/>
+      <c r="M129" s="92"/>
+      <c r="N129" s="92"/>
+      <c r="O129" s="92"/>
+      <c r="P129" s="94"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="G130" s="77"/>
-      <c r="H130" s="87"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
+      <c r="A130" s="86"/>
+      <c r="B130" s="95"/>
+      <c r="C130" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="D130" s="97"/>
+      <c r="E130" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="F130" s="6"/>
+      <c r="G130" s="42"/>
+      <c r="H130" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="I130" s="6"/>
+      <c r="J130" s="100"/>
+      <c r="K130" s="100"/>
+      <c r="L130" s="100"/>
+      <c r="M130" s="100"/>
+      <c r="N130" s="100"/>
+      <c r="O130" s="100"/>
+      <c r="P130" s="101"/>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="86"/>
+      <c r="B131" s="95"/>
+      <c r="C131" s="102" t="s">
+        <v>55</v>
+      </c>
+      <c r="D131" s="97"/>
+      <c r="E131" s="103" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,5,0)</f>
+        <v>Administrador</v>
+      </c>
+      <c r="F131" s="6"/>
+      <c r="G131" s="97"/>
+      <c r="H131" s="104" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,11,0)</f>
+        <v>En proceso</v>
+      </c>
+      <c r="I131" s="6"/>
+      <c r="J131" s="97"/>
+      <c r="K131" s="100"/>
+      <c r="L131" s="100"/>
+      <c r="M131" s="100"/>
+      <c r="N131" s="100"/>
+      <c r="O131" s="100"/>
+      <c r="P131" s="101"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="86"/>
+      <c r="B132" s="95"/>
+      <c r="C132" s="97"/>
+      <c r="D132" s="97"/>
+      <c r="E132" s="97"/>
+      <c r="F132" s="97"/>
+      <c r="G132" s="97"/>
+      <c r="H132" s="97"/>
+      <c r="I132" s="97"/>
+      <c r="J132" s="97"/>
+      <c r="K132" s="97"/>
+      <c r="L132" s="97"/>
+      <c r="M132" s="100"/>
+      <c r="N132" s="97"/>
+      <c r="O132" s="97"/>
+      <c r="P132" s="101"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="86"/>
+      <c r="B133" s="95"/>
+      <c r="C133" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D133" s="97"/>
+      <c r="E133" s="98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="6"/>
+      <c r="G133" s="97"/>
+      <c r="H133" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="I133" s="6"/>
+      <c r="J133" s="97"/>
+      <c r="K133" s="97"/>
+      <c r="L133" s="97"/>
+      <c r="M133" s="100"/>
+      <c r="N133" s="97"/>
+      <c r="O133" s="97"/>
+      <c r="P133" s="101"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="86"/>
+      <c r="B134" s="95"/>
+      <c r="C134" s="105">
+        <f>VLOOKUP('Historia de Usuario'!C131,'Formato descripción HU'!B11:O138,8,0)</f>
+        <v>8</v>
+      </c>
+      <c r="D134" s="97"/>
+      <c r="E134" s="103" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,10,0)</f>
+        <v>Alta</v>
+      </c>
+      <c r="F134" s="6"/>
+      <c r="G134" s="97"/>
+      <c r="H134" s="103" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,7,0)</f>
+        <v>Alexander Toapanta</v>
+      </c>
+      <c r="I134" s="6"/>
+      <c r="J134" s="97"/>
+      <c r="K134" s="97"/>
+      <c r="L134" s="97"/>
+      <c r="M134" s="100"/>
+      <c r="N134" s="97"/>
+      <c r="O134" s="97"/>
+      <c r="P134" s="101"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="86"/>
+      <c r="B135" s="95"/>
+      <c r="C135" s="100"/>
+      <c r="D135" s="97"/>
+      <c r="E135" s="100"/>
+      <c r="F135" s="100"/>
+      <c r="G135" s="97"/>
+      <c r="H135" s="97"/>
+      <c r="I135" s="100"/>
+      <c r="J135" s="100"/>
+      <c r="K135" s="100"/>
+      <c r="L135" s="100"/>
+      <c r="M135" s="100"/>
+      <c r="N135" s="100"/>
+      <c r="O135" s="100"/>
+      <c r="P135" s="101"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="86"/>
+      <c r="B136" s="95"/>
+      <c r="C136" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D136" s="107" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,3,0)</f>
+        <v>Obtener información consolidada del gimnasio</v>
+      </c>
+      <c r="E136" s="53"/>
+      <c r="F136" s="100"/>
+      <c r="G136" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="H136" s="107" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,4,0)</f>
+        <v>Apoyar la toma de decisiones</v>
+      </c>
+      <c r="I136" s="55"/>
+      <c r="J136" s="53"/>
+      <c r="K136" s="100"/>
+      <c r="L136" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="M136" s="108" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,6,0)</f>
+        <v>Generar reportes de asistencia, pagos y membresías</v>
+      </c>
+      <c r="N136" s="55"/>
+      <c r="O136" s="53"/>
+      <c r="P136" s="101"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="86"/>
+      <c r="B137" s="95"/>
+      <c r="C137" s="57"/>
+      <c r="D137" s="58"/>
+      <c r="E137" s="59"/>
+      <c r="F137" s="100"/>
+      <c r="G137" s="57"/>
+      <c r="H137" s="58"/>
+      <c r="J137" s="59"/>
+      <c r="K137" s="100"/>
+      <c r="L137" s="57"/>
+      <c r="M137" s="58"/>
+      <c r="O137" s="59"/>
+      <c r="P137" s="101"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="86"/>
+      <c r="B138" s="95"/>
+      <c r="C138" s="60"/>
+      <c r="D138" s="61"/>
+      <c r="E138" s="62"/>
+      <c r="F138" s="100"/>
+      <c r="G138" s="60"/>
+      <c r="H138" s="61"/>
+      <c r="I138" s="63"/>
+      <c r="J138" s="62"/>
+      <c r="K138" s="100"/>
+      <c r="L138" s="60"/>
+      <c r="M138" s="61"/>
+      <c r="N138" s="63"/>
+      <c r="O138" s="62"/>
+      <c r="P138" s="101"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="86"/>
+      <c r="B139" s="95"/>
+      <c r="C139" s="100"/>
+      <c r="D139" s="100"/>
+      <c r="E139" s="100"/>
+      <c r="F139" s="100"/>
+      <c r="G139" s="97"/>
+      <c r="H139" s="97"/>
+      <c r="I139" s="97"/>
+      <c r="J139" s="100"/>
+      <c r="K139" s="100"/>
+      <c r="L139" s="100"/>
+      <c r="M139" s="100"/>
+      <c r="N139" s="100"/>
+      <c r="O139" s="100"/>
+      <c r="P139" s="101"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="86"/>
+      <c r="B140" s="95"/>
+      <c r="C140" s="109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D140" s="53"/>
+      <c r="E140" s="110" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,14,0)</f>
+        <v>Reportes administrativos</v>
+      </c>
+      <c r="F140" s="66"/>
+      <c r="G140" s="66"/>
+      <c r="H140" s="66"/>
+      <c r="I140" s="66"/>
+      <c r="J140" s="66"/>
+      <c r="K140" s="66"/>
+      <c r="L140" s="66"/>
+      <c r="M140" s="66"/>
+      <c r="N140" s="66"/>
+      <c r="O140" s="67"/>
+      <c r="P140" s="101"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="86"/>
+      <c r="B141" s="95"/>
+      <c r="C141" s="61"/>
+      <c r="D141" s="62"/>
+      <c r="E141" s="68"/>
+      <c r="F141" s="69"/>
+      <c r="G141" s="69"/>
+      <c r="H141" s="69"/>
+      <c r="I141" s="69"/>
+      <c r="J141" s="69"/>
+      <c r="K141" s="69"/>
+      <c r="L141" s="69"/>
+      <c r="M141" s="69"/>
+      <c r="N141" s="69"/>
+      <c r="O141" s="70"/>
+      <c r="P141" s="101"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="86"/>
+      <c r="B142" s="95"/>
+      <c r="C142" s="100"/>
+      <c r="D142" s="100"/>
+      <c r="E142" s="111"/>
+      <c r="F142" s="111"/>
+      <c r="G142" s="111"/>
+      <c r="H142" s="111"/>
+      <c r="I142" s="100"/>
+      <c r="J142" s="100"/>
+      <c r="K142" s="100"/>
+      <c r="L142" s="100"/>
+      <c r="M142" s="100"/>
+      <c r="N142" s="100"/>
+      <c r="O142" s="100"/>
+      <c r="P142" s="101"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="86"/>
+      <c r="B143" s="95"/>
+      <c r="C143" s="112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D143" s="53"/>
+      <c r="E143" s="113" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,12,0)</f>
+        <v>Verificar la generación correcta de reportes y exportación de información.</v>
+      </c>
+      <c r="F143" s="55"/>
+      <c r="G143" s="55"/>
+      <c r="H143" s="53"/>
+      <c r="I143" s="114"/>
+      <c r="J143" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="K143" s="53"/>
+      <c r="L143" s="115" t="str">
+        <f>VLOOKUP(C131,'Formato descripción HU'!B11:O138,13,0)</f>
+        <v>Requiere información proveniente de los módulos de usuarios, pagos y reservas.</v>
+      </c>
+      <c r="M143" s="55"/>
+      <c r="N143" s="55"/>
+      <c r="O143" s="53"/>
+      <c r="P143" s="101"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="86"/>
+      <c r="B144" s="95"/>
+      <c r="C144" s="58"/>
+      <c r="D144" s="59"/>
+      <c r="E144" s="58"/>
+      <c r="H144" s="59"/>
+      <c r="I144" s="114"/>
+      <c r="J144" s="58"/>
+      <c r="K144" s="59"/>
+      <c r="L144" s="58"/>
+      <c r="O144" s="59"/>
+      <c r="P144" s="101"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="86"/>
+      <c r="B145" s="95"/>
+      <c r="C145" s="61"/>
+      <c r="D145" s="62"/>
+      <c r="E145" s="61"/>
+      <c r="F145" s="63"/>
+      <c r="G145" s="63"/>
+      <c r="H145" s="62"/>
+      <c r="I145" s="114"/>
+      <c r="J145" s="61"/>
+      <c r="K145" s="62"/>
+      <c r="L145" s="61"/>
+      <c r="M145" s="63"/>
+      <c r="N145" s="63"/>
+      <c r="O145" s="62"/>
+      <c r="P145" s="101"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="86"/>
+      <c r="B146" s="116"/>
+      <c r="C146" s="117"/>
+      <c r="D146" s="117"/>
+      <c r="E146" s="118"/>
+      <c r="F146" s="118"/>
+      <c r="G146" s="118"/>
+      <c r="H146" s="118"/>
+      <c r="I146" s="117"/>
+      <c r="J146" s="117"/>
+      <c r="K146" s="117"/>
+      <c r="L146" s="117"/>
+      <c r="M146" s="117"/>
+      <c r="N146" s="117"/>
+      <c r="O146" s="117"/>
+      <c r="P146" s="119"/>
+    </row>
     <row r="147" ht="15.75" customHeight="1"/>
     <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="86"/>
+      <c r="B149" s="86"/>
+      <c r="C149" s="87"/>
+      <c r="D149" s="87"/>
+      <c r="E149" s="87"/>
+      <c r="F149" s="86"/>
+      <c r="G149" s="86"/>
+      <c r="H149" s="86"/>
+      <c r="I149" s="86"/>
+      <c r="J149" s="86"/>
+      <c r="K149" s="86"/>
+      <c r="L149" s="86"/>
+      <c r="M149" s="86"/>
+      <c r="N149" s="86"/>
+      <c r="O149" s="86"/>
+      <c r="P149" s="86"/>
+    </row>
+    <row r="150" ht="29.25" customHeight="1">
+      <c r="A150" s="86"/>
+      <c r="B150" s="88" t="s">
+        <v>112</v>
+      </c>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="5"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5"/>
+      <c r="P150" s="6"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="86"/>
+      <c r="B151" s="86"/>
+      <c r="C151" s="87"/>
+      <c r="D151" s="87"/>
+      <c r="E151" s="87"/>
+      <c r="F151" s="87"/>
+      <c r="G151" s="87"/>
+      <c r="H151" s="87"/>
+      <c r="I151" s="87"/>
+      <c r="J151" s="87"/>
+      <c r="K151" s="87"/>
+      <c r="L151" s="87"/>
+      <c r="M151" s="87"/>
+      <c r="N151" s="87"/>
+      <c r="O151" s="87"/>
+      <c r="P151" s="86"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="86"/>
+      <c r="B152" s="90"/>
+      <c r="C152" s="91"/>
+      <c r="D152" s="91"/>
+      <c r="E152" s="91"/>
+      <c r="F152" s="92"/>
+      <c r="G152" s="92"/>
+      <c r="H152" s="92"/>
+      <c r="I152" s="92"/>
+      <c r="J152" s="92"/>
+      <c r="K152" s="92"/>
+      <c r="L152" s="92"/>
+      <c r="M152" s="92"/>
+      <c r="N152" s="92"/>
+      <c r="O152" s="92"/>
+      <c r="P152" s="94"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="86"/>
+      <c r="B153" s="95"/>
+      <c r="C153" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="D153" s="97"/>
+      <c r="E153" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="F153" s="6"/>
+      <c r="G153" s="97"/>
+      <c r="H153" s="98" t="s">
+        <v>11</v>
+      </c>
+      <c r="I153" s="6"/>
+      <c r="J153" s="100"/>
+      <c r="K153" s="100"/>
+      <c r="L153" s="100"/>
+      <c r="M153" s="100"/>
+      <c r="N153" s="100"/>
+      <c r="O153" s="100"/>
+      <c r="P153" s="101"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="86"/>
+      <c r="B154" s="95"/>
+      <c r="C154" s="102" t="s">
+        <v>63</v>
+      </c>
+      <c r="D154" s="97"/>
+      <c r="E154" s="103" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,5,0)</f>
+        <v>Atleta</v>
+      </c>
+      <c r="F154" s="6"/>
+      <c r="G154" s="97"/>
+      <c r="H154" s="104" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,11,0)</f>
+        <v>En proceso</v>
+      </c>
+      <c r="I154" s="6"/>
+      <c r="J154" s="97"/>
+      <c r="K154" s="100"/>
+      <c r="L154" s="100"/>
+      <c r="M154" s="100"/>
+      <c r="N154" s="100"/>
+      <c r="O154" s="100"/>
+      <c r="P154" s="101"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="86"/>
+      <c r="B155" s="95"/>
+      <c r="C155" s="97"/>
+      <c r="D155" s="97"/>
+      <c r="E155" s="97"/>
+      <c r="F155" s="97"/>
+      <c r="G155" s="97"/>
+      <c r="H155" s="97"/>
+      <c r="I155" s="97"/>
+      <c r="J155" s="97"/>
+      <c r="K155" s="97"/>
+      <c r="L155" s="97"/>
+      <c r="M155" s="100"/>
+      <c r="N155" s="97"/>
+      <c r="O155" s="97"/>
+      <c r="P155" s="101"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="86"/>
+      <c r="B156" s="95"/>
+      <c r="C156" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D156" s="97"/>
+      <c r="E156" s="98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156" s="6"/>
+      <c r="G156" s="97"/>
+      <c r="H156" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="I156" s="6"/>
+      <c r="J156" s="97"/>
+      <c r="K156" s="97"/>
+      <c r="L156" s="97"/>
+      <c r="M156" s="100"/>
+      <c r="N156" s="97"/>
+      <c r="O156" s="97"/>
+      <c r="P156" s="101"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="86"/>
+      <c r="B157" s="95"/>
+      <c r="C157" s="105">
+        <f>VLOOKUP('Historia de Usuario'!C154,'Formato descripción HU'!B12:O161,8,0)</f>
+        <v>10</v>
+      </c>
+      <c r="D157" s="97"/>
+      <c r="E157" s="103" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,10,0)</f>
+        <v>Media </v>
+      </c>
+      <c r="F157" s="6"/>
+      <c r="G157" s="97"/>
+      <c r="H157" s="103" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,7,0)</f>
+        <v>Kenned Sigcha</v>
+      </c>
+      <c r="I157" s="6"/>
+      <c r="J157" s="97"/>
+      <c r="K157" s="97"/>
+      <c r="L157" s="97"/>
+      <c r="M157" s="100"/>
+      <c r="N157" s="97"/>
+      <c r="O157" s="97"/>
+      <c r="P157" s="101"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="86"/>
+      <c r="B158" s="95"/>
+      <c r="C158" s="100"/>
+      <c r="D158" s="97"/>
+      <c r="E158" s="100"/>
+      <c r="F158" s="100"/>
+      <c r="G158" s="97"/>
+      <c r="H158" s="97"/>
+      <c r="I158" s="100"/>
+      <c r="J158" s="100"/>
+      <c r="K158" s="100"/>
+      <c r="L158" s="100"/>
+      <c r="M158" s="100"/>
+      <c r="N158" s="100"/>
+      <c r="O158" s="100"/>
+      <c r="P158" s="101"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="86"/>
+      <c r="B159" s="95"/>
+      <c r="C159" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D159" s="107" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,3,0)</f>
+        <v>Sincronizar información deportiva automáticamente</v>
+      </c>
+      <c r="E159" s="53"/>
+      <c r="F159" s="100"/>
+      <c r="G159" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="H159" s="107" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,4,0)</f>
+        <v>Automatizar el seguimiento físico de los atletas</v>
+      </c>
+      <c r="I159" s="55"/>
+      <c r="J159" s="53"/>
+      <c r="K159" s="100"/>
+      <c r="L159" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="M159" s="108" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,6,0)</f>
+        <v>Conectar aplicaciones externas y sincronizar datos biométricos</v>
+      </c>
+      <c r="N159" s="55"/>
+      <c r="O159" s="53"/>
+      <c r="P159" s="101"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="86"/>
+      <c r="B160" s="95"/>
+      <c r="C160" s="57"/>
+      <c r="D160" s="58"/>
+      <c r="E160" s="59"/>
+      <c r="F160" s="100"/>
+      <c r="G160" s="57"/>
+      <c r="H160" s="58"/>
+      <c r="J160" s="59"/>
+      <c r="K160" s="100"/>
+      <c r="L160" s="57"/>
+      <c r="M160" s="58"/>
+      <c r="O160" s="59"/>
+      <c r="P160" s="101"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="86"/>
+      <c r="B161" s="95"/>
+      <c r="C161" s="60"/>
+      <c r="D161" s="61"/>
+      <c r="E161" s="62"/>
+      <c r="F161" s="100"/>
+      <c r="G161" s="60"/>
+      <c r="H161" s="61"/>
+      <c r="I161" s="63"/>
+      <c r="J161" s="62"/>
+      <c r="K161" s="100"/>
+      <c r="L161" s="60"/>
+      <c r="M161" s="61"/>
+      <c r="N161" s="63"/>
+      <c r="O161" s="62"/>
+      <c r="P161" s="101"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="86"/>
+      <c r="B162" s="95"/>
+      <c r="C162" s="100"/>
+      <c r="D162" s="100"/>
+      <c r="E162" s="100"/>
+      <c r="F162" s="100"/>
+      <c r="G162" s="97"/>
+      <c r="H162" s="97"/>
+      <c r="I162" s="97"/>
+      <c r="J162" s="100"/>
+      <c r="K162" s="100"/>
+      <c r="L162" s="100"/>
+      <c r="M162" s="100"/>
+      <c r="N162" s="100"/>
+      <c r="O162" s="100"/>
+      <c r="P162" s="101"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="86"/>
+      <c r="B163" s="95"/>
+      <c r="C163" s="109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D163" s="53"/>
+      <c r="E163" s="110" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,14,0)</f>
+        <v>Integración con aplicaciones de salud</v>
+      </c>
+      <c r="F163" s="66"/>
+      <c r="G163" s="66"/>
+      <c r="H163" s="66"/>
+      <c r="I163" s="66"/>
+      <c r="J163" s="66"/>
+      <c r="K163" s="66"/>
+      <c r="L163" s="66"/>
+      <c r="M163" s="66"/>
+      <c r="N163" s="66"/>
+      <c r="O163" s="67"/>
+      <c r="P163" s="101"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="86"/>
+      <c r="B164" s="95"/>
+      <c r="C164" s="61"/>
+      <c r="D164" s="62"/>
+      <c r="E164" s="68"/>
+      <c r="F164" s="69"/>
+      <c r="G164" s="69"/>
+      <c r="H164" s="69"/>
+      <c r="I164" s="69"/>
+      <c r="J164" s="69"/>
+      <c r="K164" s="69"/>
+      <c r="L164" s="69"/>
+      <c r="M164" s="69"/>
+      <c r="N164" s="69"/>
+      <c r="O164" s="70"/>
+      <c r="P164" s="101"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="86"/>
+      <c r="B165" s="95"/>
+      <c r="C165" s="100"/>
+      <c r="D165" s="100"/>
+      <c r="E165" s="111"/>
+      <c r="F165" s="111"/>
+      <c r="G165" s="111"/>
+      <c r="H165" s="111"/>
+      <c r="I165" s="100"/>
+      <c r="J165" s="100"/>
+      <c r="K165" s="100"/>
+      <c r="L165" s="100"/>
+      <c r="M165" s="100"/>
+      <c r="N165" s="100"/>
+      <c r="O165" s="100"/>
+      <c r="P165" s="101"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="86"/>
+      <c r="B166" s="95"/>
+      <c r="C166" s="112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D166" s="53"/>
+      <c r="E166" s="113" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,12,0)</f>
+        <v>Verificar la importación correcta de datos desde Google Fit, Samsung Health o Apple Health.</v>
+      </c>
+      <c r="F166" s="55"/>
+      <c r="G166" s="55"/>
+      <c r="H166" s="53"/>
+      <c r="I166" s="114"/>
+      <c r="J166" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="K166" s="53"/>
+      <c r="L166" s="115" t="str">
+        <f>VLOOKUP(C154,'Formato descripción HU'!B12:O161,13,0)</f>
+        <v>Riesgo asociado a cambios en APIs externas y restricciones de acceso de terceros.</v>
+      </c>
+      <c r="M166" s="55"/>
+      <c r="N166" s="55"/>
+      <c r="O166" s="53"/>
+      <c r="P166" s="101"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="86"/>
+      <c r="B167" s="95"/>
+      <c r="C167" s="58"/>
+      <c r="D167" s="59"/>
+      <c r="E167" s="58"/>
+      <c r="H167" s="59"/>
+      <c r="I167" s="114"/>
+      <c r="J167" s="58"/>
+      <c r="K167" s="59"/>
+      <c r="L167" s="58"/>
+      <c r="O167" s="59"/>
+      <c r="P167" s="101"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="86"/>
+      <c r="B168" s="95"/>
+      <c r="C168" s="61"/>
+      <c r="D168" s="62"/>
+      <c r="E168" s="61"/>
+      <c r="F168" s="63"/>
+      <c r="G168" s="63"/>
+      <c r="H168" s="62"/>
+      <c r="I168" s="114"/>
+      <c r="J168" s="61"/>
+      <c r="K168" s="62"/>
+      <c r="L168" s="61"/>
+      <c r="M168" s="63"/>
+      <c r="N168" s="63"/>
+      <c r="O168" s="62"/>
+      <c r="P168" s="101"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="86"/>
+      <c r="B169" s="116"/>
+      <c r="C169" s="117"/>
+      <c r="D169" s="117"/>
+      <c r="E169" s="118"/>
+      <c r="F169" s="118"/>
+      <c r="G169" s="118"/>
+      <c r="H169" s="118"/>
+      <c r="I169" s="117"/>
+      <c r="J169" s="117"/>
+      <c r="K169" s="117"/>
+      <c r="L169" s="117"/>
+      <c r="M169" s="117"/>
+      <c r="N169" s="117"/>
+      <c r="O169" s="117"/>
+      <c r="P169" s="119"/>
+    </row>
     <row r="170" ht="15.75" customHeight="1"/>
     <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="86"/>
+      <c r="B172" s="86"/>
+      <c r="C172" s="87"/>
+      <c r="D172" s="87"/>
+      <c r="E172" s="87"/>
+      <c r="F172" s="86"/>
+      <c r="G172" s="86"/>
+      <c r="H172" s="86"/>
+      <c r="I172" s="86"/>
+      <c r="J172" s="86"/>
+      <c r="K172" s="86"/>
+      <c r="L172" s="86"/>
+      <c r="M172" s="86"/>
+      <c r="N172" s="86"/>
+      <c r="O172" s="86"/>
+      <c r="P172" s="86"/>
+    </row>
+    <row r="173" ht="27.75" customHeight="1">
+      <c r="A173" s="86"/>
+      <c r="B173" s="88" t="s">
+        <v>113</v>
+      </c>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
+      <c r="J173" s="5"/>
+      <c r="K173" s="5"/>
+      <c r="L173" s="5"/>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5"/>
+      <c r="P173" s="6"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="86"/>
+      <c r="B174" s="86"/>
+      <c r="C174" s="87"/>
+      <c r="D174" s="87"/>
+      <c r="E174" s="87"/>
+      <c r="F174" s="87"/>
+      <c r="G174" s="87"/>
+      <c r="H174" s="87"/>
+      <c r="I174" s="87"/>
+      <c r="J174" s="87"/>
+      <c r="K174" s="87"/>
+      <c r="L174" s="87"/>
+      <c r="M174" s="87"/>
+      <c r="N174" s="87"/>
+      <c r="O174" s="87"/>
+      <c r="P174" s="86"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="86"/>
+      <c r="B175" s="90"/>
+      <c r="C175" s="91"/>
+      <c r="D175" s="91"/>
+      <c r="E175" s="91"/>
+      <c r="F175" s="92"/>
+      <c r="G175" s="92"/>
+      <c r="H175" s="92"/>
+      <c r="I175" s="92"/>
+      <c r="J175" s="92"/>
+      <c r="K175" s="92"/>
+      <c r="L175" s="92"/>
+      <c r="M175" s="92"/>
+      <c r="N175" s="92"/>
+      <c r="O175" s="92"/>
+      <c r="P175" s="94"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="86"/>
+      <c r="B176" s="95"/>
+      <c r="C176" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="D176" s="97"/>
+      <c r="E176" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="F176" s="6"/>
+      <c r="G176" s="97"/>
+      <c r="H176" s="98" t="s">
+        <v>11</v>
+      </c>
+      <c r="I176" s="6"/>
+      <c r="J176" s="100"/>
+      <c r="K176" s="100"/>
+      <c r="L176" s="100"/>
+      <c r="M176" s="100"/>
+      <c r="N176" s="100"/>
+      <c r="O176" s="100"/>
+      <c r="P176" s="101"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="86"/>
+      <c r="B177" s="95"/>
+      <c r="C177" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="D177" s="97"/>
+      <c r="E177" s="103" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,5,0)</f>
+        <v>Administrador</v>
+      </c>
+      <c r="F177" s="6"/>
+      <c r="G177" s="97"/>
+      <c r="H177" s="104" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,11,0)</f>
+        <v>En proceso</v>
+      </c>
+      <c r="I177" s="6"/>
+      <c r="J177" s="97"/>
+      <c r="K177" s="100"/>
+      <c r="L177" s="100"/>
+      <c r="M177" s="100"/>
+      <c r="N177" s="100"/>
+      <c r="O177" s="100"/>
+      <c r="P177" s="101"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="86"/>
+      <c r="B178" s="95"/>
+      <c r="C178" s="97"/>
+      <c r="D178" s="97"/>
+      <c r="E178" s="97"/>
+      <c r="F178" s="97"/>
+      <c r="G178" s="97"/>
+      <c r="H178" s="97"/>
+      <c r="I178" s="97"/>
+      <c r="J178" s="97"/>
+      <c r="K178" s="97"/>
+      <c r="L178" s="97"/>
+      <c r="M178" s="100"/>
+      <c r="N178" s="97"/>
+      <c r="O178" s="97"/>
+      <c r="P178" s="101"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="86"/>
+      <c r="B179" s="95"/>
+      <c r="C179" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D179" s="97"/>
+      <c r="E179" s="98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" s="6"/>
+      <c r="G179" s="97"/>
+      <c r="H179" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="I179" s="6"/>
+      <c r="J179" s="97"/>
+      <c r="K179" s="97"/>
+      <c r="L179" s="97"/>
+      <c r="M179" s="100"/>
+      <c r="N179" s="97"/>
+      <c r="O179" s="97"/>
+      <c r="P179" s="101"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="86"/>
+      <c r="B180" s="95"/>
+      <c r="C180" s="105">
+        <f>VLOOKUP('Historia de Usuario'!C177,'Formato descripción HU'!B13:O184,8,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D180" s="97"/>
+      <c r="E180" s="103" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,10,0)</f>
+        <v>Media </v>
+      </c>
+      <c r="F180" s="6"/>
+      <c r="G180" s="97"/>
+      <c r="H180" s="103" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,7,0)</f>
+        <v>Alexander Toapanta</v>
+      </c>
+      <c r="I180" s="6"/>
+      <c r="J180" s="97"/>
+      <c r="K180" s="97"/>
+      <c r="L180" s="97"/>
+      <c r="M180" s="100"/>
+      <c r="N180" s="97"/>
+      <c r="O180" s="97"/>
+      <c r="P180" s="101"/>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="86"/>
+      <c r="B181" s="95"/>
+      <c r="C181" s="100"/>
+      <c r="D181" s="97"/>
+      <c r="E181" s="100"/>
+      <c r="F181" s="100"/>
+      <c r="G181" s="97"/>
+      <c r="H181" s="97"/>
+      <c r="I181" s="100"/>
+      <c r="J181" s="100"/>
+      <c r="K181" s="100"/>
+      <c r="L181" s="100"/>
+      <c r="M181" s="100"/>
+      <c r="N181" s="100"/>
+      <c r="O181" s="100"/>
+      <c r="P181" s="101"/>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="86"/>
+      <c r="B182" s="95"/>
+      <c r="C182" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D182" s="107" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,3,0)</f>
+        <v>Facilitar el análisis y respaldo de datos</v>
+      </c>
+      <c r="E182" s="53"/>
+      <c r="F182" s="100"/>
+      <c r="G182" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="H182" s="107" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,4,0)</f>
+        <v>Permitir compartir información fuera del sistema</v>
+      </c>
+      <c r="I182" s="55"/>
+      <c r="J182" s="53"/>
+      <c r="K182" s="100"/>
+      <c r="L182" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="M182" s="108" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,6,0)</f>
+        <v>Exportar reportes y registros en PDF y CSV</v>
+      </c>
+      <c r="N182" s="55"/>
+      <c r="O182" s="53"/>
+      <c r="P182" s="101"/>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="86"/>
+      <c r="B183" s="95"/>
+      <c r="C183" s="57"/>
+      <c r="D183" s="58"/>
+      <c r="E183" s="59"/>
+      <c r="F183" s="100"/>
+      <c r="G183" s="57"/>
+      <c r="H183" s="58"/>
+      <c r="J183" s="59"/>
+      <c r="K183" s="100"/>
+      <c r="L183" s="57"/>
+      <c r="M183" s="58"/>
+      <c r="O183" s="59"/>
+      <c r="P183" s="101"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="86"/>
+      <c r="B184" s="95"/>
+      <c r="C184" s="60"/>
+      <c r="D184" s="61"/>
+      <c r="E184" s="62"/>
+      <c r="F184" s="100"/>
+      <c r="G184" s="60"/>
+      <c r="H184" s="61"/>
+      <c r="I184" s="63"/>
+      <c r="J184" s="62"/>
+      <c r="K184" s="100"/>
+      <c r="L184" s="60"/>
+      <c r="M184" s="61"/>
+      <c r="N184" s="63"/>
+      <c r="O184" s="62"/>
+      <c r="P184" s="101"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="86"/>
+      <c r="B185" s="95"/>
+      <c r="C185" s="100"/>
+      <c r="D185" s="100"/>
+      <c r="E185" s="100"/>
+      <c r="F185" s="100"/>
+      <c r="G185" s="97"/>
+      <c r="H185" s="97"/>
+      <c r="I185" s="97"/>
+      <c r="J185" s="100"/>
+      <c r="K185" s="100"/>
+      <c r="L185" s="100"/>
+      <c r="M185" s="100"/>
+      <c r="N185" s="100"/>
+      <c r="O185" s="100"/>
+      <c r="P185" s="101"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="86"/>
+      <c r="B186" s="95"/>
+      <c r="C186" s="109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D186" s="53"/>
+      <c r="E186" s="110" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,14,0)</f>
+        <v>Exportación de información</v>
+      </c>
+      <c r="F186" s="66"/>
+      <c r="G186" s="66"/>
+      <c r="H186" s="66"/>
+      <c r="I186" s="66"/>
+      <c r="J186" s="66"/>
+      <c r="K186" s="66"/>
+      <c r="L186" s="66"/>
+      <c r="M186" s="66"/>
+      <c r="N186" s="66"/>
+      <c r="O186" s="67"/>
+      <c r="P186" s="101"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="86"/>
+      <c r="B187" s="95"/>
+      <c r="C187" s="61"/>
+      <c r="D187" s="62"/>
+      <c r="E187" s="68"/>
+      <c r="F187" s="69"/>
+      <c r="G187" s="69"/>
+      <c r="H187" s="69"/>
+      <c r="I187" s="69"/>
+      <c r="J187" s="69"/>
+      <c r="K187" s="69"/>
+      <c r="L187" s="69"/>
+      <c r="M187" s="69"/>
+      <c r="N187" s="69"/>
+      <c r="O187" s="70"/>
+      <c r="P187" s="101"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="86"/>
+      <c r="B188" s="95"/>
+      <c r="C188" s="100"/>
+      <c r="D188" s="100"/>
+      <c r="E188" s="111"/>
+      <c r="F188" s="111"/>
+      <c r="G188" s="111"/>
+      <c r="H188" s="111"/>
+      <c r="I188" s="100"/>
+      <c r="J188" s="100"/>
+      <c r="K188" s="100"/>
+      <c r="L188" s="100"/>
+      <c r="M188" s="100"/>
+      <c r="N188" s="100"/>
+      <c r="O188" s="100"/>
+      <c r="P188" s="101"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="86"/>
+      <c r="B189" s="95"/>
+      <c r="C189" s="112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D189" s="53"/>
+      <c r="E189" s="113" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,12,0)</f>
+        <v>Verificar la generación y descarga correcta de archivos PDF y CSV.</v>
+      </c>
+      <c r="F189" s="55"/>
+      <c r="G189" s="55"/>
+      <c r="H189" s="53"/>
+      <c r="I189" s="114"/>
+      <c r="J189" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="K189" s="53"/>
+      <c r="L189" s="115" t="str">
+        <f>VLOOKUP(C177,'Formato descripción HU'!B13:O184,13,0)</f>
+        <v>Depende de la correcta implementación de los módulos de reportes y consultas.</v>
+      </c>
+      <c r="M189" s="55"/>
+      <c r="N189" s="55"/>
+      <c r="O189" s="53"/>
+      <c r="P189" s="101"/>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="86"/>
+      <c r="B190" s="95"/>
+      <c r="C190" s="58"/>
+      <c r="D190" s="59"/>
+      <c r="E190" s="58"/>
+      <c r="H190" s="59"/>
+      <c r="I190" s="114"/>
+      <c r="J190" s="58"/>
+      <c r="K190" s="59"/>
+      <c r="L190" s="58"/>
+      <c r="O190" s="59"/>
+      <c r="P190" s="101"/>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="86"/>
+      <c r="B191" s="95"/>
+      <c r="C191" s="61"/>
+      <c r="D191" s="62"/>
+      <c r="E191" s="61"/>
+      <c r="F191" s="63"/>
+      <c r="G191" s="63"/>
+      <c r="H191" s="62"/>
+      <c r="I191" s="114"/>
+      <c r="J191" s="61"/>
+      <c r="K191" s="62"/>
+      <c r="L191" s="61"/>
+      <c r="M191" s="63"/>
+      <c r="N191" s="63"/>
+      <c r="O191" s="62"/>
+      <c r="P191" s="101"/>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="86"/>
+      <c r="B192" s="116"/>
+      <c r="C192" s="117"/>
+      <c r="D192" s="117"/>
+      <c r="E192" s="118"/>
+      <c r="F192" s="118"/>
+      <c r="G192" s="118"/>
+      <c r="H192" s="118"/>
+      <c r="I192" s="117"/>
+      <c r="J192" s="117"/>
+      <c r="K192" s="117"/>
+      <c r="L192" s="117"/>
+      <c r="M192" s="117"/>
+      <c r="N192" s="117"/>
+      <c r="O192" s="117"/>
+      <c r="P192" s="119"/>
+    </row>
     <row r="193" ht="15.75" customHeight="1"/>
     <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="86"/>
+      <c r="B195" s="86"/>
+      <c r="C195" s="87"/>
+      <c r="D195" s="87"/>
+      <c r="E195" s="87"/>
+      <c r="F195" s="86"/>
+      <c r="G195" s="86"/>
+      <c r="H195" s="86"/>
+      <c r="I195" s="86"/>
+      <c r="J195" s="86"/>
+      <c r="K195" s="86"/>
+      <c r="L195" s="86"/>
+      <c r="M195" s="86"/>
+      <c r="N195" s="86"/>
+      <c r="O195" s="86"/>
+      <c r="P195" s="86"/>
+    </row>
+    <row r="196" ht="30.0" customHeight="1">
+      <c r="A196" s="86"/>
+      <c r="B196" s="88" t="s">
+        <v>114</v>
+      </c>
+      <c r="C196" s="5"/>
+      <c r="D196" s="5"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="5"/>
+      <c r="H196" s="5"/>
+      <c r="I196" s="5"/>
+      <c r="J196" s="5"/>
+      <c r="K196" s="5"/>
+      <c r="L196" s="5"/>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+      <c r="O196" s="5"/>
+      <c r="P196" s="6"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="86"/>
+      <c r="B197" s="86"/>
+      <c r="C197" s="87"/>
+      <c r="D197" s="87"/>
+      <c r="E197" s="87"/>
+      <c r="F197" s="87"/>
+      <c r="G197" s="87"/>
+      <c r="H197" s="87"/>
+      <c r="I197" s="87"/>
+      <c r="J197" s="87"/>
+      <c r="K197" s="87"/>
+      <c r="L197" s="87"/>
+      <c r="M197" s="87"/>
+      <c r="N197" s="87"/>
+      <c r="O197" s="87"/>
+      <c r="P197" s="86"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="86"/>
+      <c r="B198" s="90"/>
+      <c r="C198" s="91"/>
+      <c r="D198" s="91"/>
+      <c r="E198" s="91"/>
+      <c r="F198" s="92"/>
+      <c r="G198" s="92"/>
+      <c r="H198" s="92"/>
+      <c r="I198" s="92"/>
+      <c r="J198" s="92"/>
+      <c r="K198" s="92"/>
+      <c r="L198" s="92"/>
+      <c r="M198" s="92"/>
+      <c r="N198" s="92"/>
+      <c r="O198" s="92"/>
+      <c r="P198" s="94"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="86"/>
+      <c r="B199" s="95"/>
+      <c r="C199" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="D199" s="97"/>
+      <c r="E199" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="F199" s="6"/>
+      <c r="G199" s="97"/>
+      <c r="H199" s="98" t="s">
+        <v>11</v>
+      </c>
+      <c r="I199" s="6"/>
+      <c r="J199" s="100"/>
+      <c r="K199" s="100"/>
+      <c r="L199" s="100"/>
+      <c r="M199" s="100"/>
+      <c r="N199" s="100"/>
+      <c r="O199" s="100"/>
+      <c r="P199" s="101"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="86"/>
+      <c r="B200" s="95"/>
+      <c r="C200" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="D200" s="97"/>
+      <c r="E200" s="103" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,5,0)</f>
+        <v>Administrador</v>
+      </c>
+      <c r="F200" s="6"/>
+      <c r="G200" s="97"/>
+      <c r="H200" s="104" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,11,0)</f>
+        <v>En proceso</v>
+      </c>
+      <c r="I200" s="6"/>
+      <c r="J200" s="97"/>
+      <c r="K200" s="100"/>
+      <c r="L200" s="100"/>
+      <c r="M200" s="100"/>
+      <c r="N200" s="100"/>
+      <c r="O200" s="100"/>
+      <c r="P200" s="101"/>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="86"/>
+      <c r="B201" s="95"/>
+      <c r="C201" s="97"/>
+      <c r="D201" s="97"/>
+      <c r="E201" s="97"/>
+      <c r="F201" s="97"/>
+      <c r="G201" s="97"/>
+      <c r="H201" s="97"/>
+      <c r="I201" s="97"/>
+      <c r="J201" s="97"/>
+      <c r="K201" s="97"/>
+      <c r="L201" s="97"/>
+      <c r="M201" s="100"/>
+      <c r="N201" s="97"/>
+      <c r="O201" s="97"/>
+      <c r="P201" s="101"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="86"/>
+      <c r="B202" s="95"/>
+      <c r="C202" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D202" s="97"/>
+      <c r="E202" s="98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="6"/>
+      <c r="G202" s="97"/>
+      <c r="H202" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="I202" s="6"/>
+      <c r="J202" s="97"/>
+      <c r="K202" s="97"/>
+      <c r="L202" s="97"/>
+      <c r="M202" s="100"/>
+      <c r="N202" s="97"/>
+      <c r="O202" s="97"/>
+      <c r="P202" s="101"/>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="86"/>
+      <c r="B203" s="95"/>
+      <c r="C203" s="105">
+        <f>VLOOKUP('Historia de Usuario'!C200,'Formato descripción HU'!B14:O207,8,0)</f>
+        <v>8</v>
+      </c>
+      <c r="D203" s="97"/>
+      <c r="E203" s="103" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,10,0)</f>
+        <v>Media </v>
+      </c>
+      <c r="F203" s="6"/>
+      <c r="G203" s="97"/>
+      <c r="H203" s="103" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,7,0)</f>
+        <v>Josué Solano</v>
+      </c>
+      <c r="I203" s="6"/>
+      <c r="J203" s="97"/>
+      <c r="K203" s="97"/>
+      <c r="L203" s="97"/>
+      <c r="M203" s="100"/>
+      <c r="N203" s="97"/>
+      <c r="O203" s="97"/>
+      <c r="P203" s="101"/>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="86"/>
+      <c r="B204" s="95"/>
+      <c r="C204" s="100"/>
+      <c r="D204" s="97"/>
+      <c r="E204" s="100"/>
+      <c r="F204" s="100"/>
+      <c r="G204" s="97"/>
+      <c r="H204" s="97"/>
+      <c r="I204" s="100"/>
+      <c r="J204" s="100"/>
+      <c r="K204" s="100"/>
+      <c r="L204" s="100"/>
+      <c r="M204" s="100"/>
+      <c r="N204" s="100"/>
+      <c r="O204" s="100"/>
+      <c r="P204" s="101"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="86"/>
+      <c r="B205" s="95"/>
+      <c r="C205" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D205" s="107" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,3,0)</f>
+        <v>Visualizar métricas clave del gimnasio</v>
+      </c>
+      <c r="E205" s="53"/>
+      <c r="F205" s="100"/>
+      <c r="G205" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="H205" s="107" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,4,0)</f>
+        <v>Apoyar la gestión administrativa</v>
+      </c>
+      <c r="I205" s="55"/>
+      <c r="J205" s="53"/>
+      <c r="K205" s="100"/>
+      <c r="L205" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="M205" s="108" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,6,0)</f>
+        <v>Mostrar estadísticas de membresías, asistencia e ingresos</v>
+      </c>
+      <c r="N205" s="55"/>
+      <c r="O205" s="53"/>
+      <c r="P205" s="101"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="86"/>
+      <c r="B206" s="95"/>
+      <c r="C206" s="57"/>
+      <c r="D206" s="58"/>
+      <c r="E206" s="59"/>
+      <c r="F206" s="100"/>
+      <c r="G206" s="57"/>
+      <c r="H206" s="58"/>
+      <c r="J206" s="59"/>
+      <c r="K206" s="100"/>
+      <c r="L206" s="57"/>
+      <c r="M206" s="58"/>
+      <c r="O206" s="59"/>
+      <c r="P206" s="101"/>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="A207" s="86"/>
+      <c r="B207" s="95"/>
+      <c r="C207" s="60"/>
+      <c r="D207" s="61"/>
+      <c r="E207" s="62"/>
+      <c r="F207" s="100"/>
+      <c r="G207" s="60"/>
+      <c r="H207" s="61"/>
+      <c r="I207" s="63"/>
+      <c r="J207" s="62"/>
+      <c r="K207" s="100"/>
+      <c r="L207" s="60"/>
+      <c r="M207" s="61"/>
+      <c r="N207" s="63"/>
+      <c r="O207" s="62"/>
+      <c r="P207" s="101"/>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="A208" s="86"/>
+      <c r="B208" s="95"/>
+      <c r="C208" s="100"/>
+      <c r="D208" s="100"/>
+      <c r="E208" s="100"/>
+      <c r="F208" s="100"/>
+      <c r="G208" s="97"/>
+      <c r="H208" s="97"/>
+      <c r="I208" s="97"/>
+      <c r="J208" s="100"/>
+      <c r="K208" s="100"/>
+      <c r="L208" s="100"/>
+      <c r="M208" s="100"/>
+      <c r="N208" s="100"/>
+      <c r="O208" s="100"/>
+      <c r="P208" s="101"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="A209" s="86"/>
+      <c r="B209" s="95"/>
+      <c r="C209" s="109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D209" s="53"/>
+      <c r="E209" s="110" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,14,0)</f>
+        <v>Dashboard de indicadores</v>
+      </c>
+      <c r="F209" s="66"/>
+      <c r="G209" s="66"/>
+      <c r="H209" s="66"/>
+      <c r="I209" s="66"/>
+      <c r="J209" s="66"/>
+      <c r="K209" s="66"/>
+      <c r="L209" s="66"/>
+      <c r="M209" s="66"/>
+      <c r="N209" s="66"/>
+      <c r="O209" s="67"/>
+      <c r="P209" s="101"/>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="A210" s="86"/>
+      <c r="B210" s="95"/>
+      <c r="C210" s="61"/>
+      <c r="D210" s="62"/>
+      <c r="E210" s="68"/>
+      <c r="F210" s="69"/>
+      <c r="G210" s="69"/>
+      <c r="H210" s="69"/>
+      <c r="I210" s="69"/>
+      <c r="J210" s="69"/>
+      <c r="K210" s="69"/>
+      <c r="L210" s="69"/>
+      <c r="M210" s="69"/>
+      <c r="N210" s="69"/>
+      <c r="O210" s="70"/>
+      <c r="P210" s="101"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="A211" s="86"/>
+      <c r="B211" s="95"/>
+      <c r="C211" s="100"/>
+      <c r="D211" s="100"/>
+      <c r="E211" s="111"/>
+      <c r="F211" s="111"/>
+      <c r="G211" s="111"/>
+      <c r="H211" s="111"/>
+      <c r="I211" s="100"/>
+      <c r="J211" s="100"/>
+      <c r="K211" s="100"/>
+      <c r="L211" s="100"/>
+      <c r="M211" s="100"/>
+      <c r="N211" s="100"/>
+      <c r="O211" s="100"/>
+      <c r="P211" s="101"/>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="A212" s="86"/>
+      <c r="B212" s="95"/>
+      <c r="C212" s="112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D212" s="53"/>
+      <c r="E212" s="113" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,12,0)</f>
+        <v>Verificar la visualización correcta de indicadores y actualización de métricas.</v>
+      </c>
+      <c r="F212" s="55"/>
+      <c r="G212" s="55"/>
+      <c r="H212" s="53"/>
+      <c r="I212" s="114"/>
+      <c r="J212" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="K212" s="53"/>
+      <c r="L212" s="115" t="str">
+        <f>VLOOKUP(C200,'Formato descripción HU'!B14:O207,13,0)</f>
+        <v>Requiere datos consolidados provenientes de todos los módulos principales del sistema.</v>
+      </c>
+      <c r="M212" s="55"/>
+      <c r="N212" s="55"/>
+      <c r="O212" s="53"/>
+      <c r="P212" s="101"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="A213" s="86"/>
+      <c r="B213" s="95"/>
+      <c r="C213" s="58"/>
+      <c r="D213" s="59"/>
+      <c r="E213" s="58"/>
+      <c r="H213" s="59"/>
+      <c r="I213" s="114"/>
+      <c r="J213" s="58"/>
+      <c r="K213" s="59"/>
+      <c r="L213" s="58"/>
+      <c r="O213" s="59"/>
+      <c r="P213" s="101"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="A214" s="86"/>
+      <c r="B214" s="95"/>
+      <c r="C214" s="61"/>
+      <c r="D214" s="62"/>
+      <c r="E214" s="61"/>
+      <c r="F214" s="63"/>
+      <c r="G214" s="63"/>
+      <c r="H214" s="62"/>
+      <c r="I214" s="114"/>
+      <c r="J214" s="61"/>
+      <c r="K214" s="62"/>
+      <c r="L214" s="61"/>
+      <c r="M214" s="63"/>
+      <c r="N214" s="63"/>
+      <c r="O214" s="62"/>
+      <c r="P214" s="101"/>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="A215" s="86"/>
+      <c r="B215" s="116"/>
+      <c r="C215" s="117"/>
+      <c r="D215" s="117"/>
+      <c r="E215" s="118"/>
+      <c r="F215" s="118"/>
+      <c r="G215" s="118"/>
+      <c r="H215" s="118"/>
+      <c r="I215" s="117"/>
+      <c r="J215" s="117"/>
+      <c r="K215" s="117"/>
+      <c r="L215" s="117"/>
+      <c r="M215" s="117"/>
+      <c r="N215" s="117"/>
+      <c r="O215" s="117"/>
+      <c r="P215" s="119"/>
+    </row>
     <row r="216" ht="15.75" customHeight="1"/>
     <row r="217" ht="15.75" customHeight="1"/>
     <row r="218" ht="15.75" customHeight="1"/>
@@ -32756,48 +34861,7 @@
     <row r="1012" ht="15.75" customHeight="1"/>
     <row r="1013" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="L66:L68"/>
-    <mergeCell ref="M66:O68"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="D66:E68"/>
-    <mergeCell ref="G66:G68"/>
-    <mergeCell ref="H66:J68"/>
-    <mergeCell ref="C70:D71"/>
-    <mergeCell ref="E70:O71"/>
-    <mergeCell ref="C73:D75"/>
-    <mergeCell ref="E73:H75"/>
-    <mergeCell ref="J73:K75"/>
-    <mergeCell ref="L73:O75"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="B81:P81"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="L90:L92"/>
-    <mergeCell ref="M90:O92"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="D90:E92"/>
-    <mergeCell ref="G90:G92"/>
-    <mergeCell ref="H90:J92"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="B105:P105"/>
-    <mergeCell ref="C94:D95"/>
-    <mergeCell ref="E94:O95"/>
-    <mergeCell ref="C97:D99"/>
-    <mergeCell ref="E97:H99"/>
-    <mergeCell ref="J97:K99"/>
-    <mergeCell ref="L97:O99"/>
-    <mergeCell ref="E101:F101"/>
+  <mergeCells count="195">
     <mergeCell ref="B6:P6"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="H9:I9"/>
@@ -32848,29 +34912,174 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="H61:I61"/>
     <mergeCell ref="H63:I63"/>
+    <mergeCell ref="L66:L68"/>
+    <mergeCell ref="M66:O68"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="D66:E68"/>
+    <mergeCell ref="G66:G68"/>
+    <mergeCell ref="H66:J68"/>
+    <mergeCell ref="C70:D71"/>
+    <mergeCell ref="E70:O71"/>
+    <mergeCell ref="C73:D75"/>
+    <mergeCell ref="E73:H75"/>
+    <mergeCell ref="J73:K75"/>
+    <mergeCell ref="L73:O75"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="B81:P81"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="L90:L92"/>
+    <mergeCell ref="M90:O92"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="D90:E92"/>
+    <mergeCell ref="G90:G92"/>
+    <mergeCell ref="H90:J92"/>
+    <mergeCell ref="C94:D95"/>
+    <mergeCell ref="E94:O95"/>
+    <mergeCell ref="C97:D99"/>
+    <mergeCell ref="E97:H99"/>
+    <mergeCell ref="J97:K99"/>
+    <mergeCell ref="L97:O99"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="H111:I111"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="B104:P104"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="H110:I110"/>
+    <mergeCell ref="L113:L115"/>
+    <mergeCell ref="M113:O115"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:E115"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="H113:J115"/>
+    <mergeCell ref="E117:O118"/>
+    <mergeCell ref="C117:D118"/>
+    <mergeCell ref="C120:D122"/>
+    <mergeCell ref="E120:H122"/>
+    <mergeCell ref="J120:K122"/>
+    <mergeCell ref="L120:O122"/>
+    <mergeCell ref="B127:P127"/>
+    <mergeCell ref="H130:I130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="H133:I133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="C182:C184"/>
+    <mergeCell ref="D182:E184"/>
+    <mergeCell ref="G182:G184"/>
+    <mergeCell ref="H182:J184"/>
+    <mergeCell ref="L182:L184"/>
+    <mergeCell ref="M182:O184"/>
+    <mergeCell ref="E186:O187"/>
+    <mergeCell ref="C186:D187"/>
+    <mergeCell ref="C189:D191"/>
+    <mergeCell ref="E189:H191"/>
+    <mergeCell ref="J189:K191"/>
+    <mergeCell ref="L189:O191"/>
+    <mergeCell ref="B196:P196"/>
+    <mergeCell ref="H199:I199"/>
+    <mergeCell ref="C209:D210"/>
+    <mergeCell ref="C212:D214"/>
+    <mergeCell ref="E212:H214"/>
+    <mergeCell ref="J212:K214"/>
+    <mergeCell ref="L212:O214"/>
+    <mergeCell ref="C205:C207"/>
+    <mergeCell ref="D205:E207"/>
+    <mergeCell ref="G205:G207"/>
+    <mergeCell ref="H205:J207"/>
+    <mergeCell ref="L205:L207"/>
+    <mergeCell ref="M205:O207"/>
+    <mergeCell ref="E209:O210"/>
+    <mergeCell ref="C136:C138"/>
+    <mergeCell ref="D136:E138"/>
+    <mergeCell ref="G136:G138"/>
+    <mergeCell ref="H136:J138"/>
+    <mergeCell ref="L136:L138"/>
+    <mergeCell ref="M136:O138"/>
+    <mergeCell ref="E140:O141"/>
+    <mergeCell ref="C140:D141"/>
+    <mergeCell ref="C143:D145"/>
+    <mergeCell ref="E143:H145"/>
+    <mergeCell ref="J143:K145"/>
+    <mergeCell ref="L143:O145"/>
+    <mergeCell ref="B150:P150"/>
+    <mergeCell ref="H153:I153"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="H154:I154"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="H156:I156"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="H157:I157"/>
+    <mergeCell ref="C159:C161"/>
+    <mergeCell ref="D159:E161"/>
+    <mergeCell ref="G159:G161"/>
+    <mergeCell ref="H159:J161"/>
+    <mergeCell ref="L159:L161"/>
+    <mergeCell ref="M159:O161"/>
+    <mergeCell ref="E163:O164"/>
+    <mergeCell ref="C163:D164"/>
+    <mergeCell ref="C166:D168"/>
+    <mergeCell ref="E166:H168"/>
+    <mergeCell ref="J166:K168"/>
+    <mergeCell ref="L166:O168"/>
+    <mergeCell ref="B173:P173"/>
+    <mergeCell ref="H176:I176"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="H177:I177"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="H179:I179"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="H180:I180"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="E200:F200"/>
+    <mergeCell ref="H200:I200"/>
+    <mergeCell ref="E202:F202"/>
+    <mergeCell ref="H202:I202"/>
+    <mergeCell ref="E203:F203"/>
+    <mergeCell ref="H203:I203"/>
   </mergeCells>
-  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86">
+  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86 I106 J106:J107 H108:I109">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Atrasado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86">
+  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86 I106 J106:J107 H108:I109">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Terminado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86">
+  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86 I106 J106:J107 H108:I109">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"En proceso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86">
+  <conditionalFormatting sqref="H10:I11 I35 J35:J36 H37:I38 I59 J59:J60 H61:I62 I83 J83:J84 H85:I86 I106 J106:J107 H108:I109">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"No Iniciado"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C10:C11 C37:C38 C61:C62 C85:C86 H128:H129">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C10:C11 C37:C38 C61:C62 C85:C86 C108:C109 H128:H129 C131:C132 C154:C155 C177:C178 C200:C201">
       <formula1>'Formato descripción HU'!$B$6:$B$17</formula1>
     </dataValidation>
   </dataValidations>
